--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126646</v>
+        <v>122126645</v>
       </c>
       <c r="B4" t="n">
         <v>56285</v>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492425</v>
+        <v>492427</v>
       </c>
       <c r="R4" t="n">
-        <v>6280751</v>
+        <v>6280750</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126650</v>
+        <v>122126647</v>
       </c>
       <c r="B5" t="n">
         <v>56285</v>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492412</v>
+        <v>492422</v>
       </c>
       <c r="R5" t="n">
-        <v>6280722</v>
+        <v>6280750</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1207,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126651</v>
+        <v>122126650</v>
       </c>
       <c r="B6" t="n">
         <v>56285</v>
@@ -1264,7 +1264,7 @@
         <v>492412</v>
       </c>
       <c r="R6" t="n">
-        <v>6280720</v>
+        <v>6280722</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126647</v>
+        <v>122126646</v>
       </c>
       <c r="B7" t="n">
         <v>56285</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492422</v>
+        <v>492425</v>
       </c>
       <c r="R7" t="n">
-        <v>6280750</v>
+        <v>6280751</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1495,7 +1495,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126645</v>
+        <v>122126648</v>
       </c>
       <c r="B8" t="n">
         <v>56285</v>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492427</v>
+        <v>492417</v>
       </c>
       <c r="R8" t="n">
         <v>6280750</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126648</v>
+        <v>122126651</v>
       </c>
       <c r="B9" t="n">
         <v>56285</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492417</v>
+        <v>492412</v>
       </c>
       <c r="R9" t="n">
-        <v>6280750</v>
+        <v>6280720</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:41</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126645</v>
+        <v>122126646</v>
       </c>
       <c r="B4" t="n">
         <v>56285</v>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492427</v>
+        <v>492425</v>
       </c>
       <c r="R4" t="n">
-        <v>6280750</v>
+        <v>6280751</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126647</v>
+        <v>122126650</v>
       </c>
       <c r="B5" t="n">
         <v>56285</v>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492422</v>
+        <v>492412</v>
       </c>
       <c r="R5" t="n">
-        <v>6280750</v>
+        <v>6280722</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>22:41</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1207,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126650</v>
+        <v>122126648</v>
       </c>
       <c r="B6" t="n">
         <v>56285</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492412</v>
+        <v>492417</v>
       </c>
       <c r="R6" t="n">
-        <v>6280722</v>
+        <v>6280750</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1351,7 +1351,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126646</v>
+        <v>122126645</v>
       </c>
       <c r="B7" t="n">
         <v>56285</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492425</v>
+        <v>492427</v>
       </c>
       <c r="R7" t="n">
-        <v>6280751</v>
+        <v>6280750</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1495,7 +1495,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126648</v>
+        <v>122126651</v>
       </c>
       <c r="B8" t="n">
         <v>56285</v>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492417</v>
+        <v>492412</v>
       </c>
       <c r="R8" t="n">
-        <v>6280750</v>
+        <v>6280720</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:41</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1639,7 +1639,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126651</v>
+        <v>122126647</v>
       </c>
       <c r="B9" t="n">
         <v>56285</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492412</v>
+        <v>492422</v>
       </c>
       <c r="R9" t="n">
-        <v>6280720</v>
+        <v>6280750</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126646</v>
+        <v>122126647</v>
       </c>
       <c r="B4" t="n">
         <v>56285</v>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492425</v>
+        <v>492422</v>
       </c>
       <c r="R4" t="n">
-        <v>6280751</v>
+        <v>6280750</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126645</v>
+        <v>122126646</v>
       </c>
       <c r="B7" t="n">
         <v>56285</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492427</v>
+        <v>492425</v>
       </c>
       <c r="R7" t="n">
-        <v>6280750</v>
+        <v>6280751</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1495,7 +1495,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126651</v>
+        <v>122126645</v>
       </c>
       <c r="B8" t="n">
         <v>56285</v>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492412</v>
+        <v>492427</v>
       </c>
       <c r="R8" t="n">
-        <v>6280720</v>
+        <v>6280750</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1639,7 +1639,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126647</v>
+        <v>122126651</v>
       </c>
       <c r="B9" t="n">
         <v>56285</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492422</v>
+        <v>492412</v>
       </c>
       <c r="R9" t="n">
-        <v>6280750</v>
+        <v>6280720</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:41</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126647</v>
+        <v>122126650</v>
       </c>
       <c r="B4" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492422</v>
+        <v>492412</v>
       </c>
       <c r="R4" t="n">
-        <v>6280750</v>
+        <v>6280722</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:41</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1063,10 +1063,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126650</v>
+        <v>122126647</v>
       </c>
       <c r="B5" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492412</v>
+        <v>492422</v>
       </c>
       <c r="R5" t="n">
-        <v>6280722</v>
+        <v>6280750</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1210,7 +1210,7 @@
         <v>122126648</v>
       </c>
       <c r="B6" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126646</v>
+        <v>122126645</v>
       </c>
       <c r="B7" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492425</v>
+        <v>492427</v>
       </c>
       <c r="R7" t="n">
-        <v>6280751</v>
+        <v>6280750</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126645</v>
+        <v>122126651</v>
       </c>
       <c r="B8" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492427</v>
+        <v>492412</v>
       </c>
       <c r="R8" t="n">
-        <v>6280750</v>
+        <v>6280720</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:41</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126651</v>
+        <v>122126646</v>
       </c>
       <c r="B9" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492412</v>
+        <v>492425</v>
       </c>
       <c r="R9" t="n">
-        <v>6280720</v>
+        <v>6280751</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126650</v>
+        <v>122126646</v>
       </c>
       <c r="B4" t="n">
         <v>56290</v>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492412</v>
+        <v>492425</v>
       </c>
       <c r="R4" t="n">
-        <v>6280722</v>
+        <v>6280751</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1063,7 +1063,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126647</v>
+        <v>122126645</v>
       </c>
       <c r="B5" t="n">
         <v>56290</v>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492422</v>
+        <v>492427</v>
       </c>
       <c r="R5" t="n">
         <v>6280750</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126648</v>
+        <v>122126651</v>
       </c>
       <c r="B6" t="n">
         <v>56290</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492417</v>
+        <v>492412</v>
       </c>
       <c r="R6" t="n">
-        <v>6280750</v>
+        <v>6280720</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:41</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1351,7 +1351,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126645</v>
+        <v>122126648</v>
       </c>
       <c r="B7" t="n">
         <v>56290</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492427</v>
+        <v>492417</v>
       </c>
       <c r="R7" t="n">
         <v>6280750</v>
@@ -1495,7 +1495,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126651</v>
+        <v>122126650</v>
       </c>
       <c r="B8" t="n">
         <v>56290</v>
@@ -1552,7 +1552,7 @@
         <v>492412</v>
       </c>
       <c r="R8" t="n">
-        <v>6280720</v>
+        <v>6280722</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126646</v>
+        <v>122126647</v>
       </c>
       <c r="B9" t="n">
         <v>56290</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492425</v>
+        <v>492422</v>
       </c>
       <c r="R9" t="n">
-        <v>6280751</v>
+        <v>6280750</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -937,11 +937,6 @@
       <c r="E4" t="n">
         <v>205995</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -1063,7 +1058,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126645</v>
+        <v>122126647</v>
       </c>
       <c r="B5" t="n">
         <v>56290</v>
@@ -1081,11 +1076,6 @@
       <c r="E5" t="n">
         <v>205995</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -1117,7 +1107,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492427</v>
+        <v>492422</v>
       </c>
       <c r="R5" t="n">
         <v>6280750</v>
@@ -1207,7 +1197,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126651</v>
+        <v>122126648</v>
       </c>
       <c r="B6" t="n">
         <v>56290</v>
@@ -1225,11 +1215,6 @@
       <c r="E6" t="n">
         <v>205995</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -1261,10 +1246,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492412</v>
+        <v>492417</v>
       </c>
       <c r="R6" t="n">
-        <v>6280720</v>
+        <v>6280750</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1296,7 +1281,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1306,7 +1291,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1351,7 +1336,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126648</v>
+        <v>122126645</v>
       </c>
       <c r="B7" t="n">
         <v>56290</v>
@@ -1369,11 +1354,6 @@
       <c r="E7" t="n">
         <v>205995</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -1405,7 +1385,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492417</v>
+        <v>492427</v>
       </c>
       <c r="R7" t="n">
         <v>6280750</v>
@@ -1513,11 +1493,6 @@
       <c r="E8" t="n">
         <v>205995</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -1639,7 +1614,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126647</v>
+        <v>122126651</v>
       </c>
       <c r="B9" t="n">
         <v>56290</v>
@@ -1657,11 +1632,6 @@
       <c r="E9" t="n">
         <v>205995</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -1693,10 +1663,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492422</v>
+        <v>492412</v>
       </c>
       <c r="R9" t="n">
-        <v>6280750</v>
+        <v>6280720</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1728,7 +1698,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1738,7 +1708,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:41</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126646</v>
+        <v>122126651</v>
       </c>
       <c r="B4" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,6 +937,11 @@
       <c r="E4" t="n">
         <v>205995</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -968,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492425</v>
+        <v>492412</v>
       </c>
       <c r="R4" t="n">
-        <v>6280751</v>
+        <v>6280720</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:41</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1058,10 +1063,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126647</v>
+        <v>122126648</v>
       </c>
       <c r="B5" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,6 +1081,11 @@
       <c r="E5" t="n">
         <v>205995</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -1107,7 +1117,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492422</v>
+        <v>492417</v>
       </c>
       <c r="R5" t="n">
         <v>6280750</v>
@@ -1197,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126648</v>
+        <v>122126650</v>
       </c>
       <c r="B6" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,6 +1225,11 @@
       <c r="E6" t="n">
         <v>205995</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -1246,10 +1261,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492417</v>
+        <v>492412</v>
       </c>
       <c r="R6" t="n">
-        <v>6280750</v>
+        <v>6280722</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1281,7 +1296,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1291,7 +1306,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:41</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1339,7 +1354,7 @@
         <v>122126645</v>
       </c>
       <c r="B7" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1353,6 +1368,11 @@
       </c>
       <c r="E7" t="n">
         <v>205995</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1475,10 +1495,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126650</v>
+        <v>122126647</v>
       </c>
       <c r="B8" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1493,6 +1513,11 @@
       <c r="E8" t="n">
         <v>205995</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -1524,10 +1549,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492412</v>
+        <v>492422</v>
       </c>
       <c r="R8" t="n">
-        <v>6280722</v>
+        <v>6280750</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1559,7 +1584,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1569,7 +1594,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1614,10 +1639,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126651</v>
+        <v>122126646</v>
       </c>
       <c r="B9" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1632,6 +1657,11 @@
       <c r="E9" t="n">
         <v>205995</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -1663,10 +1693,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492412</v>
+        <v>492425</v>
       </c>
       <c r="R9" t="n">
-        <v>6280720</v>
+        <v>6280751</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1698,7 +1728,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1708,7 +1738,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126651</v>
+        <v>122126645</v>
       </c>
       <c r="B4" t="n">
         <v>56294</v>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492412</v>
+        <v>492427</v>
       </c>
       <c r="R4" t="n">
-        <v>6280720</v>
+        <v>6280750</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1063,7 +1063,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126648</v>
+        <v>122126646</v>
       </c>
       <c r="B5" t="n">
         <v>56294</v>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492417</v>
+        <v>492425</v>
       </c>
       <c r="R5" t="n">
-        <v>6280750</v>
+        <v>6280751</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126650</v>
+        <v>122126651</v>
       </c>
       <c r="B6" t="n">
         <v>56294</v>
@@ -1264,7 +1264,7 @@
         <v>492412</v>
       </c>
       <c r="R6" t="n">
-        <v>6280722</v>
+        <v>6280720</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126645</v>
+        <v>122126648</v>
       </c>
       <c r="B7" t="n">
         <v>56294</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492427</v>
+        <v>492417</v>
       </c>
       <c r="R7" t="n">
         <v>6280750</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126646</v>
+        <v>122126650</v>
       </c>
       <c r="B9" t="n">
         <v>56294</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492425</v>
+        <v>492412</v>
       </c>
       <c r="R9" t="n">
-        <v>6280751</v>
+        <v>6280722</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:41</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1781,6 +1781,125 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127664065</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58166</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>492541</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6280716</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -1786,7 +1786,7 @@
         <v>127664065</v>
       </c>
       <c r="B10" t="n">
-        <v>58166</v>
+        <v>58168</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -1786,7 +1786,7 @@
         <v>127664065</v>
       </c>
       <c r="B10" t="n">
-        <v>58168</v>
+        <v>58171</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -1786,7 +1786,7 @@
         <v>127664065</v>
       </c>
       <c r="B10" t="n">
-        <v>58171</v>
+        <v>58177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -1786,7 +1786,7 @@
         <v>127664065</v>
       </c>
       <c r="B10" t="n">
-        <v>58177</v>
+        <v>58178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88301583</v>
+        <v>108482805</v>
       </c>
       <c r="B2" t="n">
-        <v>100516</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>225046</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492541.3429989877</v>
+        <v>492541</v>
       </c>
       <c r="R2" t="n">
-        <v>6280715.766568603</v>
+        <v>6280716</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist, Per Fogelström</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -799,12 +787,7 @@
         <v>118464227</v>
       </c>
       <c r="B3" t="n">
-        <v>57387</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,15 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122126645</v>
+        <v>127664065</v>
       </c>
       <c r="B4" t="n">
-        <v>56294</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,51 +913,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492427</v>
+        <v>492541</v>
       </c>
       <c r="R4" t="n">
-        <v>6280750</v>
+        <v>6280716</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,27 +979,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,43 +1006,25 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126646</v>
+        <v>122126645</v>
       </c>
       <c r="B5" t="n">
-        <v>56294</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492425</v>
+        <v>492427</v>
       </c>
       <c r="R5" t="n">
-        <v>6280751</v>
+        <v>6280750</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1207,15 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126651</v>
+        <v>122126646</v>
       </c>
       <c r="B6" t="n">
-        <v>56294</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492412</v>
+        <v>492425</v>
       </c>
       <c r="R6" t="n">
-        <v>6280720</v>
+        <v>6280751</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1296,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1306,7 +1254,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1351,15 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126648</v>
+        <v>122126647</v>
       </c>
       <c r="B7" t="n">
-        <v>56294</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1348,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492417</v>
+        <v>492422</v>
       </c>
       <c r="R7" t="n">
         <v>6280750</v>
@@ -1495,15 +1438,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126647</v>
+        <v>122126648</v>
       </c>
       <c r="B8" t="n">
-        <v>56294</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1487,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492422</v>
+        <v>492417</v>
       </c>
       <c r="R8" t="n">
         <v>6280750</v>
@@ -1639,15 +1577,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126650</v>
+        <v>122126649</v>
       </c>
       <c r="B9" t="n">
-        <v>56294</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,10 +1626,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492412</v>
+        <v>492404</v>
       </c>
       <c r="R9" t="n">
-        <v>6280722</v>
+        <v>6280718</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1783,122 +1716,387 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127664065</v>
+        <v>122126650</v>
       </c>
       <c r="B10" t="n">
-        <v>58178</v>
+        <v>56835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102995</v>
+        <v>205995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>492412</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6280722</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122126651</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>492412</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6280720</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>88301583</v>
+      </c>
+      <c r="B12" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q12" t="n">
         <v>492541</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R12" t="n">
         <v>6280716</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S12" t="n">
         <v>25</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Kronoberg</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Tingsryd</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Småland</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Väckelsång</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-10-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-10-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
         <is>
           <t>Tomas Lundqvist</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Tomas Lundqvist</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Fogelström, Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118464227</v>
+        <v>135252425</v>
       </c>
       <c r="B3" t="n">
-        <v>58039</v>
+        <v>57280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,53 +795,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102626</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492541</v>
+        <v>492488</v>
       </c>
       <c r="R3" t="n">
-        <v>6280716</v>
+        <v>6280803</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,17 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rishögarna efter björkarna</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,22 +881,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127664065</v>
+        <v>135252427</v>
       </c>
       <c r="B4" t="n">
-        <v>58463</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>100082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -945,17 +936,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492541</v>
+        <v>492488</v>
       </c>
       <c r="R4" t="n">
-        <v>6280716</v>
+        <v>6280803</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +990,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126645</v>
+        <v>118464227</v>
       </c>
       <c r="B5" t="n">
-        <v>56835</v>
+        <v>58039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,51 +1013,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492427</v>
+        <v>492541</v>
       </c>
       <c r="R5" t="n">
-        <v>6280750</v>
+        <v>6280716</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,27 +1083,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22:40</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>22:41</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Calluna AB</t>
+          <t>Rishögarna efter björkarna</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,38 +1105,25 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126646</v>
+        <v>135252540</v>
       </c>
       <c r="B6" t="n">
-        <v>56835</v>
+        <v>58061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,48 +1131,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>102626</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492425</v>
+        <v>492488</v>
       </c>
       <c r="R6" t="n">
-        <v>6280751</v>
+        <v>6280803</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1239,27 +1194,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>22:40</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>22:41</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,87 +1211,72 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126647</v>
+        <v>135252530</v>
       </c>
       <c r="B7" t="n">
-        <v>56835</v>
+        <v>57796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>102976</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492422</v>
+        <v>492488</v>
       </c>
       <c r="R7" t="n">
-        <v>6280750</v>
+        <v>6280803</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1378,27 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>22:40</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>22:41</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,87 +1320,72 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126648</v>
+        <v>135252523</v>
       </c>
       <c r="B8" t="n">
-        <v>56835</v>
+        <v>58231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>102980</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492417</v>
+        <v>492488</v>
       </c>
       <c r="R8" t="n">
-        <v>6280750</v>
+        <v>6280803</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1517,27 +1412,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>22:40</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>22:41</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1549,87 +1429,72 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126649</v>
+        <v>135252529</v>
       </c>
       <c r="B9" t="n">
-        <v>56835</v>
+        <v>58234</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205995</v>
+        <v>102981</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492404</v>
+        <v>492488</v>
       </c>
       <c r="R9" t="n">
-        <v>6280718</v>
+        <v>6280803</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1656,27 +1521,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>22:35</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>22:36</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1688,38 +1538,25 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122126650</v>
+        <v>127664065</v>
       </c>
       <c r="B10" t="n">
-        <v>56835</v>
+        <v>58463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,51 +1564,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205995</v>
+        <v>102995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492412</v>
+        <v>492541</v>
       </c>
       <c r="R10" t="n">
-        <v>6280722</v>
+        <v>6280716</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1795,27 +1630,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:36</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1827,87 +1657,72 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122126651</v>
+        <v>135252431</v>
       </c>
       <c r="B11" t="n">
-        <v>56835</v>
+        <v>58698</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205995</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492412</v>
+        <v>492488</v>
       </c>
       <c r="R11" t="n">
-        <v>6280720</v>
+        <v>6280803</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1934,27 +1749,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>22:35</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>22:36</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1966,137 +1766,1097 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>122126645</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>492427</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6280750</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122126646</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>492425</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6280751</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122126647</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>492422</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6280750</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122126648</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>492417</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6280750</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122126649</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>492404</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6280718</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122126650</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>492412</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6280722</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122126651</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>492412</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6280720</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>88301583</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B19" t="n">
         <v>103404</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E19" t="n">
         <v>225046</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Vanlig skogsalm</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Ulmus glabra subsp. glabra</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q19" t="n">
         <v>492541</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R19" t="n">
         <v>6280716</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S19" t="n">
         <v>25</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Kronoberg</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Tingsryd</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Småland</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Väckelsång</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
         <is>
           <t>Tomas Lundqvist</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Per Fogelström, Tomas Lundqvist</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108482805</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252425</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252427</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118464227</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252540</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252530</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252523</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,6 +1590,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252529</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1669,6 +1714,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127664065</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252431</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126645</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2056,6 +2116,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126646</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2195,6 +2260,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126647</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2334,6 +2404,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126648</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2473,6 +2548,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126649</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2612,6 +2692,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126650</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2751,6 +2836,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126651</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2857,8 +2947,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88301583</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135252425</v>
       </c>
       <c r="B3" t="n">
-        <v>57280</v>
+        <v>57285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135252427</v>
       </c>
       <c r="B4" t="n">
-        <v>57912</v>
+        <v>57917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>135252540</v>
       </c>
       <c r="B6" t="n">
-        <v>58061</v>
+        <v>58066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>135252530</v>
       </c>
       <c r="B7" t="n">
-        <v>57796</v>
+        <v>57801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>135252523</v>
       </c>
       <c r="B8" t="n">
-        <v>58231</v>
+        <v>58236</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135252529</v>
       </c>
       <c r="B9" t="n">
-        <v>58234</v>
+        <v>58239</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>135252431</v>
       </c>
       <c r="B11" t="n">
-        <v>58698</v>
+        <v>58703</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49699-2023 artfynd.xlsx
+++ b/artfynd/A 49699-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118464227</v>
+        <v>135252425</v>
       </c>
       <c r="B3" t="n">
-        <v>58039</v>
+        <v>57285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,53 +805,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102626</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492541</v>
+        <v>492488</v>
       </c>
       <c r="R3" t="n">
-        <v>6280716</v>
+        <v>6280803</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,17 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rishögarna efter björkarna</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,27 +891,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118464227</t>
+          <t>https://artportalen.se/Sighting/135252425</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127664065</v>
+        <v>135252427</v>
       </c>
       <c r="B4" t="n">
-        <v>58463</v>
+        <v>57917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,16 +919,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>100082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -960,17 +951,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492541</v>
+        <v>492488</v>
       </c>
       <c r="R4" t="n">
-        <v>6280716</v>
+        <v>6280803</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,27 +1005,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127664065</t>
+          <t>https://artportalen.se/Sighting/135252427</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122126645</v>
+        <v>118464227</v>
       </c>
       <c r="B5" t="n">
-        <v>56835</v>
+        <v>58039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,51 +1033,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492427</v>
+        <v>492541</v>
       </c>
       <c r="R5" t="n">
-        <v>6280750</v>
+        <v>6280716</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,27 +1103,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22:40</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>22:41</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Calluna AB</t>
+          <t>Rishögarna efter björkarna</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,43 +1125,30 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122126645</t>
+          <t>https://artportalen.se/Sighting/118464227</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122126646</v>
+        <v>135252540</v>
       </c>
       <c r="B6" t="n">
-        <v>56835</v>
+        <v>58066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,48 +1156,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>102626</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492425</v>
+        <v>492488</v>
       </c>
       <c r="R6" t="n">
-        <v>6280751</v>
+        <v>6280803</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1264,27 +1219,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>22:40</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>22:41</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,92 +1236,77 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122126646</t>
+          <t>https://artportalen.se/Sighting/135252540</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122126647</v>
+        <v>135252530</v>
       </c>
       <c r="B7" t="n">
-        <v>56835</v>
+        <v>57801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>102976</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492422</v>
+        <v>492488</v>
       </c>
       <c r="R7" t="n">
-        <v>6280750</v>
+        <v>6280803</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1408,27 +1333,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>22:40</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>22:41</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1440,92 +1350,77 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122126647</t>
+          <t>https://artportalen.se/Sighting/135252530</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122126648</v>
+        <v>135252523</v>
       </c>
       <c r="B8" t="n">
-        <v>56835</v>
+        <v>58236</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>102980</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492417</v>
+        <v>492488</v>
       </c>
       <c r="R8" t="n">
-        <v>6280750</v>
+        <v>6280803</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1552,27 +1447,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>22:40</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>22:41</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1584,92 +1464,77 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122126648</t>
+          <t>https://artportalen.se/Sighting/135252523</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122126649</v>
+        <v>135252529</v>
       </c>
       <c r="B9" t="n">
-        <v>56835</v>
+        <v>58239</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205995</v>
+        <v>102981</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492404</v>
+        <v>492488</v>
       </c>
       <c r="R9" t="n">
-        <v>6280718</v>
+        <v>6280803</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1696,27 +1561,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>22:35</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>22:36</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1728,43 +1578,30 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122126649</t>
+          <t>https://artportalen.se/Sighting/135252529</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122126650</v>
+        <v>127664065</v>
       </c>
       <c r="B10" t="n">
-        <v>56835</v>
+        <v>58463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,51 +1609,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205995</v>
+        <v>102995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492412</v>
+        <v>492541</v>
       </c>
       <c r="R10" t="n">
-        <v>6280722</v>
+        <v>6280716</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1840,27 +1675,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:36</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1872,92 +1702,77 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122126650</t>
+          <t>https://artportalen.se/Sighting/127664065</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122126651</v>
+        <v>135812969</v>
       </c>
       <c r="B11" t="n">
-        <v>56835</v>
+        <v>58139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205995</v>
+        <v>103020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jät, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492412</v>
+        <v>492488</v>
       </c>
       <c r="R11" t="n">
-        <v>6280720</v>
+        <v>6280803</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1984,27 +1799,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>22:36</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Calluna AB</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2016,89 +1826,80 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>David Alvunger</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Ignell</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
-        </is>
-      </c>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122126651</t>
+          <t>https://artportalen.se/Sighting/135812969</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>88301583</v>
+        <v>135252431</v>
       </c>
       <c r="B12" t="n">
-        <v>103404</v>
+        <v>58703</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>225046</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
+          <t>Kvarndungen S, Lidhemssjön, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492541</v>
+        <v>492488</v>
       </c>
       <c r="R12" t="n">
-        <v>6280716</v>
+        <v>6280803</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2122,12 +1923,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-10-02</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-10-02</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2136,23 +1937,1141 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Fogelström, Tomas Lundqvist</t>
+          <t>Hugo Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252431</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122126645</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>492427</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6280750</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126645</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122126646</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>492425</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6280751</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126646</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122126647</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>492422</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6280750</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126647</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122126648</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>492417</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6280750</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126648</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122126649</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>492404</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6280718</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126649</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122126650</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>492412</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6280722</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126650</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122126651</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Jät, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>492412</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6280720</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Ignell</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122126651</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>88301583</v>
+      </c>
+      <c r="B20" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ödetomt Lidhem, Lidhemssjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>492541</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6280716</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Väckelsång</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-10-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-10-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Per Fogelström, Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/88301583</t>
         </is>
@@ -2171,6 +3090,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
